--- a/output/pdf_financials_xlsx/TINY.xlsx
+++ b/output/pdf_financials_xlsx/TINY.xlsx
@@ -3311,7 +3311,7 @@
         <v>0.842437</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>1.618113</v>
+        <v>209.227355</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>-2.784267</v>
@@ -3333,22 +3333,22 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.080626</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>3.424757</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>39.451612</v>
+        <v>43.815945</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>40.884631</v>
+        <v>46.932889</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>40.930627</v>
+        <v>47.455711</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>37.228459</v>
       </c>
     </row>
     <row r="93">
@@ -6316,7 +6316,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -9451,7 +9455,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -14565,7 +14573,11 @@
           <t>Reserve 4</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TINY.xlsx
+++ b/output/pdf_financials_xlsx/TINY.xlsx
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.5038550000000001</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>26.122247</v>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.5038550000000001</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>26.122247</v>
@@ -4226,16 +4226,16 @@
         <v>-10.7</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.4281</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.282977</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.221648</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.751146</v>
       </c>
     </row>
     <row r="125">
@@ -4254,16 +4254,16 @@
         <v>-10.7</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.4281</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.282977</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.221648</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.751146</v>
       </c>
     </row>
     <row r="126">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
@@ -16157,7 +16157,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -18323,7 +18327,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TINY.xlsx
+++ b/output/pdf_financials_xlsx/TINY.xlsx
@@ -21243,7 +21243,11 @@
           <t>Addition of intangible asset</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TINY.xlsx
+++ b/output/pdf_financials_xlsx/TINY.xlsx
@@ -1800,16 +1800,16 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.408901</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.004422</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.311511</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.014977</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -1828,16 +1828,16 @@
         <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>3.049341</v>
+        <v>3.458242</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>12.797523</v>
+        <v>12.801945</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>18.938172</v>
+        <v>19.249683</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>14.059004</v>
+        <v>14.073981</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>14.885918</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.047692</v>
+        <v>1.638791</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.08169</v>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0121</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.55789</v>
       </c>
     </row>
     <row r="111">
@@ -4000,16 +4000,16 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-3.047935</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.110729</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.030416</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.101341</v>
       </c>
     </row>
     <row r="117">
@@ -6118,7 +6118,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -9312,7 +9316,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -15085,7 +15093,11 @@
           <t>Accretion expense 13</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -16408,7 +16420,11 @@
           <t>Proceeds from share issuance 14</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -16663,7 +16679,11 @@
           <t>Purchase of intangible assets 7</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -18476,7 +18496,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -18668,7 +18692,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
